--- a/mse_results.xlsx
+++ b/mse_results.xlsx
@@ -453,30 +453,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627680595345391</v>
+        <v>0.007479766455154011</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00373218423805569</v>
+        <v>0.004007124699288123</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002027528336591165</v>
+        <v>0.001379356065735598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02627680595345391</v>
+        <v>0.007479766455154011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00373218423805569</v>
+        <v>0.004007124699288123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002027528336591165</v>
+        <v>0.001379356065735598</v>
       </c>
     </row>
   </sheetData>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B258"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,7 +510,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002401633848995831</v>
+        <v>0.004444690257916254</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002401633848995831</v>
+        <v>0.003432576837978094</v>
       </c>
     </row>
     <row r="4">
@@ -526,7 +526,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002529702390876714</v>
+        <v>0.002901500053280045</v>
       </c>
     </row>
     <row r="5">
@@ -534,7 +534,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.002593736661817155</v>
+        <v>0.002635961660931021</v>
       </c>
     </row>
     <row r="6">
@@ -542,7 +542,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.002635059554288558</v>
+        <v>0.002417054141161417</v>
       </c>
     </row>
     <row r="7">
@@ -550,7 +550,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002662608149269493</v>
+        <v>0.002259774794395522</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002670536487208733</v>
+        <v>0.00216832958666658</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002676482740663164</v>
+        <v>0.002091479366502042</v>
       </c>
     </row>
     <row r="10">
@@ -574,7 +574,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002655265637226687</v>
+        <v>0.002017371600019369</v>
       </c>
     </row>
     <row r="11">
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002638291954477506</v>
+        <v>0.001956921859983594</v>
       </c>
     </row>
     <row r="12">
@@ -590,7 +590,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002610544806394074</v>
+        <v>0.001899385104826338</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002640440743817413</v>
+        <v>0.001856716583792162</v>
       </c>
     </row>
     <row r="14">
@@ -606,7 +606,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002665737306252545</v>
+        <v>0.001822056999745663</v>
       </c>
     </row>
     <row r="15">
@@ -614,7 +614,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002645203593650604</v>
+        <v>0.001791472087917255</v>
       </c>
     </row>
     <row r="16">
@@ -622,7 +622,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00262740770939559</v>
+        <v>0.001762092959421067</v>
       </c>
     </row>
     <row r="17">
@@ -630,7 +630,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.002592454378057016</v>
+        <v>0.001741049617888215</v>
       </c>
     </row>
     <row r="18">
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00256161320334651</v>
+        <v>0.00172169070721021</v>
       </c>
     </row>
     <row r="19">
@@ -646,7 +646,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.002523172699116079</v>
+        <v>0.001701858515588441</v>
       </c>
     </row>
     <row r="20">
@@ -654,7 +654,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.002488778563752009</v>
+        <v>0.001686845133260708</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.00244675981681738</v>
+        <v>0.001669594200537122</v>
       </c>
     </row>
     <row r="22">
@@ -670,7 +670,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.002408742855305097</v>
+        <v>0.001652936564903785</v>
       </c>
     </row>
     <row r="23">
@@ -678,7 +678,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.00238304125498834</v>
+        <v>0.001639335313672103</v>
       </c>
     </row>
     <row r="24">
@@ -686,7 +686,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00235984581898275</v>
+        <v>0.001623753571223956</v>
       </c>
     </row>
     <row r="25">
@@ -694,7 +694,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.002338583335977628</v>
+        <v>0.001608426064343058</v>
       </c>
     </row>
     <row r="26">
@@ -702,7 +702,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.002343002289199204</v>
+        <v>0.001595856397767738</v>
       </c>
     </row>
     <row r="27">
@@ -710,7 +710,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.002347081322942198</v>
+        <v>0.001584185525681848</v>
       </c>
     </row>
     <row r="28">
@@ -718,7 +718,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.002340238732599795</v>
+        <v>0.001582110759021874</v>
       </c>
     </row>
     <row r="29">
@@ -726,7 +726,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.002333884898710421</v>
+        <v>0.001571148422774235</v>
       </c>
     </row>
     <row r="30">
@@ -734,7 +734,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.002320471354427477</v>
+        <v>0.001565793000316956</v>
       </c>
     </row>
     <row r="31">
@@ -742,7 +742,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.002307952046430061</v>
+        <v>0.00155534783038826</v>
       </c>
     </row>
     <row r="32">
@@ -750,7 +750,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.002301942909947682</v>
+        <v>0.001544507072914224</v>
       </c>
     </row>
     <row r="33">
@@ -758,7 +758,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.002296309344495452</v>
+        <v>0.001535098852626603</v>
       </c>
     </row>
     <row r="34">
@@ -766,7 +766,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.002275462136997003</v>
+        <v>0.001528011416228305</v>
       </c>
     </row>
     <row r="35">
@@ -774,7 +774,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.00227003462206017</v>
+        <v>0.001521243024617466</v>
       </c>
     </row>
     <row r="36">
@@ -782,7 +782,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.002264917250834013</v>
+        <v>0.001518455126506888</v>
       </c>
     </row>
     <row r="37">
@@ -790,7 +790,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.002262523323260465</v>
+        <v>0.00151563522641309</v>
       </c>
     </row>
     <row r="38">
@@ -798,7 +798,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.002260258797177379</v>
+        <v>0.001516782687538042</v>
       </c>
     </row>
     <row r="39">
@@ -806,7 +806,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.002266232848188012</v>
+        <v>0.001531199288108833</v>
       </c>
     </row>
     <row r="40">
@@ -814,7 +814,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.002271900537608355</v>
+        <v>0.001534657015495161</v>
       </c>
     </row>
     <row r="41">
@@ -822,7 +822,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.002269308287404635</v>
+        <v>0.001537094974630594</v>
       </c>
     </row>
     <row r="42">
@@ -830,7 +830,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.002266842488430365</v>
+        <v>0.001538855664663829</v>
       </c>
     </row>
     <row r="43">
@@ -838,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.002269738621528512</v>
+        <v>0.001537832027857902</v>
       </c>
     </row>
     <row r="44">
@@ -846,7 +846,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.002266971408103947</v>
+        <v>0.001539834070135008</v>
       </c>
     </row>
     <row r="45">
@@ -854,7 +854,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.002264329977107772</v>
+        <v>0.001540940102797535</v>
       </c>
     </row>
     <row r="46">
@@ -862,7 +862,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.002258591991930455</v>
+        <v>0.001542818814421945</v>
       </c>
     </row>
     <row r="47">
@@ -870,7 +870,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.002253103484369543</v>
+        <v>0.001549066450008457</v>
       </c>
     </row>
     <row r="48">
@@ -878,7 +878,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.002240663807584466</v>
+        <v>0.00154772700488209</v>
       </c>
     </row>
     <row r="49">
@@ -886,7 +886,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.002228742450665433</v>
+        <v>0.001553306645258606</v>
       </c>
     </row>
     <row r="50">
@@ -894,7 +894,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.002228906910662201</v>
+        <v>0.001554379788828673</v>
       </c>
     </row>
     <row r="51">
@@ -902,7 +902,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.002229064792259098</v>
+        <v>0.001559240108759422</v>
       </c>
     </row>
     <row r="52">
@@ -910,7 +910,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>0.002240694037642038</v>
+        <v>0.001559854811050279</v>
       </c>
     </row>
     <row r="53">
@@ -918,7 +918,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>0.002240825197149699</v>
+        <v>0.001559866196920358</v>
       </c>
     </row>
     <row r="54">
@@ -926,7 +926,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>0.002240951407241978</v>
+        <v>0.001563525197012925</v>
       </c>
     </row>
     <row r="55">
@@ -934,7 +934,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>0.002236682812654867</v>
+        <v>0.001565001723456404</v>
       </c>
     </row>
     <row r="56">
@@ -942,7 +942,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>0.002232569439689106</v>
+        <v>0.001564718729199724</v>
       </c>
     </row>
     <row r="57">
@@ -950,7 +950,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>0.002241806025791368</v>
+        <v>0.001562473861731645</v>
       </c>
     </row>
     <row r="58">
@@ -958,7 +958,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0022507185211532</v>
+        <v>0.001560307761543148</v>
       </c>
     </row>
     <row r="59">
@@ -966,7 +966,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>0.002253166943534215</v>
+        <v>0.001559182986262296</v>
       </c>
     </row>
     <row r="60">
@@ -974,7 +974,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>0.002256489951377474</v>
+        <v>0.001556495768760921</v>
       </c>
     </row>
     <row r="61">
@@ -982,7 +982,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>0.002259702192292626</v>
+        <v>0.00155413082474243</v>
       </c>
     </row>
     <row r="62">
@@ -990,7 +990,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>0.002262587078521758</v>
+        <v>0.001552461332170595</v>
       </c>
     </row>
     <row r="63">
@@ -998,7 +998,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>0.00226537890390479</v>
+        <v>0.001548836890254147</v>
       </c>
     </row>
     <row r="64">
@@ -1006,7 +1006,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>0.002268988256288402</v>
+        <v>0.001547197156899497</v>
       </c>
     </row>
     <row r="65">
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>0.002272484816410027</v>
+        <v>0.001548702343568653</v>
       </c>
     </row>
     <row r="66">
@@ -1022,7 +1022,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>0.002274941070813397</v>
+        <v>0.001551292190484999</v>
       </c>
     </row>
     <row r="67">
@@ -1030,7 +1030,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>0.002277322893265149</v>
+        <v>0.001550191402268959</v>
       </c>
     </row>
     <row r="68">
@@ -1038,7 +1038,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>0.002276708149600236</v>
+        <v>0.001549123473402653</v>
       </c>
     </row>
     <row r="69">
@@ -1046,7 +1046,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>0.002276111486631349</v>
+        <v>0.001548753527861249</v>
       </c>
     </row>
     <row r="70">
@@ -1054,7 +1054,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>0.002278578249936127</v>
+        <v>0.001548844616455615</v>
       </c>
     </row>
     <row r="71">
@@ -1062,7 +1062,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>0.002280974534289339</v>
+        <v>0.001548152036606744</v>
       </c>
     </row>
     <row r="72">
@@ -1070,7 +1070,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>0.002278654449044262</v>
+        <v>0.00154931027582931</v>
       </c>
     </row>
     <row r="73">
@@ -1078,7 +1078,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>0.002280156579537877</v>
+        <v>0.001551038478775032</v>
       </c>
     </row>
     <row r="74">
@@ -1086,7 +1086,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>0.002281617555771392</v>
+        <v>0.001551627347834379</v>
       </c>
     </row>
     <row r="75">
@@ -1094,7 +1094,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>0.002283039046160758</v>
+        <v>0.001550667051080436</v>
       </c>
     </row>
     <row r="76">
@@ -1102,7 +1102,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>0.00228442263013974</v>
+        <v>0.001548387106015732</v>
       </c>
     </row>
     <row r="77">
@@ -1110,7 +1110,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>0.002282209812399598</v>
+        <v>0.001546167159505362</v>
       </c>
     </row>
     <row r="78">
@@ -1118,7 +1118,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>0.002280054470444913</v>
+        <v>0.001544076827054213</v>
       </c>
     </row>
     <row r="79">
@@ -1126,7 +1126,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>0.00228237571960636</v>
+        <v>0.001541571097976812</v>
       </c>
     </row>
     <row r="80">
@@ -1134,7 +1134,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>0.002284638202966251</v>
+        <v>0.001538966274260813</v>
       </c>
     </row>
     <row r="81">
@@ -1142,7 +1142,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>0.002280238808387407</v>
+        <v>0.001535970654078951</v>
       </c>
     </row>
     <row r="82">
@@ -1150,7 +1150,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>0.002275948040835202</v>
+        <v>0.001533464349084527</v>
       </c>
     </row>
     <row r="83">
@@ -1158,7 +1158,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>0.002267295663684219</v>
+        <v>0.001533275196216072</v>
       </c>
     </row>
     <row r="84">
@@ -1166,7 +1166,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>0.002270668714888143</v>
+        <v>0.001533224040721571</v>
       </c>
     </row>
     <row r="85">
@@ -1174,7 +1174,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>0.002273961455349115</v>
+        <v>0.001532084622514572</v>
       </c>
     </row>
     <row r="86">
@@ -1182,7 +1182,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>0.002280340593084599</v>
+        <v>0.001530972014147738</v>
       </c>
     </row>
     <row r="87">
@@ -1190,7 +1190,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>0.002286571378779723</v>
+        <v>0.001530155842215412</v>
       </c>
     </row>
     <row r="88">
@@ -1198,7 +1198,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>0.002289567787226046</v>
+        <v>0.001528726229535655</v>
       </c>
     </row>
     <row r="89">
@@ -1206,7 +1206,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>0.002292496095480408</v>
+        <v>0.001527006166725034</v>
       </c>
     </row>
     <row r="90">
@@ -1214,7 +1214,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>0.002294596442054864</v>
+        <v>0.00152528848401297</v>
       </c>
     </row>
     <row r="91">
@@ -1222,7 +1222,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>0.002296650114260999</v>
+        <v>0.001524136993922787</v>
       </c>
     </row>
     <row r="92">
@@ -1230,7 +1230,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>0.002296130401797459</v>
+        <v>0.001521961884585202</v>
       </c>
     </row>
     <row r="93">
@@ -1238,7 +1238,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>0.002295621987430953</v>
+        <v>0.001519782202275407</v>
       </c>
     </row>
     <row r="94">
@@ -1246,7 +1246,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>0.002297880370923878</v>
+        <v>0.001518350336250226</v>
       </c>
     </row>
     <row r="95">
@@ -1254,7 +1254,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>0.002300533334143941</v>
+        <v>0.001517095787880176</v>
       </c>
     </row>
     <row r="96">
@@ -1262,7 +1262,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>0.00230313044550674</v>
+        <v>0.001515613164092951</v>
       </c>
     </row>
     <row r="97">
@@ -1270,7 +1270,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>0.002309179540533989</v>
+        <v>0.001515006621179395</v>
       </c>
     </row>
     <row r="98">
@@ -1278,7 +1278,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>0.002315103911952429</v>
+        <v>0.001516175650767625</v>
       </c>
     </row>
     <row r="99">
@@ -1286,7 +1286,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>0.002318149575880893</v>
+        <v>0.001515608583916507</v>
       </c>
     </row>
     <row r="100">
@@ -1294,7 +1294,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>0.002321133711245146</v>
+        <v>0.001515887490356567</v>
       </c>
     </row>
     <row r="101">
@@ -1302,7 +1302,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>0.002322366802592911</v>
+        <v>0.001516872630545971</v>
       </c>
     </row>
     <row r="102">
@@ -1310,7 +1310,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>0.002323575476290225</v>
+        <v>0.001517389962551363</v>
       </c>
     </row>
     <row r="103">
@@ -1318,7 +1318,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>0.002319643898328489</v>
+        <v>0.001518511532302284</v>
       </c>
     </row>
     <row r="104">
@@ -1326,7 +1326,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>0.002318332717152154</v>
+        <v>0.001518809305338914</v>
       </c>
     </row>
     <row r="105">
@@ -1334,7 +1334,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>0.002317046750998442</v>
+        <v>0.001518703705599692</v>
       </c>
     </row>
     <row r="106">
@@ -1342,7 +1342,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>0.002318636376359668</v>
+        <v>0.001519656671184501</v>
       </c>
     </row>
     <row r="107">
@@ -1350,7 +1350,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>0.002320196008789552</v>
+        <v>0.001521245811466666</v>
       </c>
     </row>
     <row r="108">
@@ -1358,7 +1358,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>0.002318887819495109</v>
+        <v>0.001521916064545329</v>
       </c>
     </row>
     <row r="109">
@@ -1366,7 +1366,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>0.002317603855928342</v>
+        <v>0.001521196591439863</v>
       </c>
     </row>
     <row r="110">
@@ -1374,7 +1374,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>0.00231433924584494</v>
+        <v>0.001520093225342245</v>
       </c>
     </row>
     <row r="111">
@@ -1382,7 +1382,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>0.002311133992308509</v>
+        <v>0.001519339043968001</v>
       </c>
     </row>
     <row r="112">
@@ -1390,7 +1390,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>0.002307986491088049</v>
+        <v>0.001519968258329349</v>
       </c>
     </row>
     <row r="113">
@@ -1398,7 +1398,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>0.002304895195246525</v>
+        <v>0.001520940841451075</v>
       </c>
     </row>
     <row r="114">
@@ -1406,7 +1406,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>0.002301858612605738</v>
+        <v>0.00152189621071224</v>
       </c>
     </row>
     <row r="115">
@@ -1414,7 +1414,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>0.002298875303344613</v>
+        <v>0.001522128600360153</v>
       </c>
     </row>
     <row r="116">
@@ -1422,7 +1422,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>0.002295943877722812</v>
+        <v>0.00152624834869602</v>
       </c>
     </row>
     <row r="117">
@@ -1430,7 +1430,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>0.002298268295281541</v>
+        <v>0.001532565279768076</v>
       </c>
     </row>
     <row r="118">
@@ -1438,7 +1438,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>0.002300552979206788</v>
+        <v>0.001537280687320309</v>
       </c>
     </row>
     <row r="119">
@@ -1446,7 +1446,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>0.002302501052755144</v>
+        <v>0.001544304118457064</v>
       </c>
     </row>
     <row r="120">
@@ -1454,7 +1454,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>0.002297306855877933</v>
+        <v>0.001548871585489612</v>
       </c>
     </row>
     <row r="121">
@@ -1462,7 +1462,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>0.002292199228948674</v>
+        <v>0.001553843551493748</v>
       </c>
     </row>
     <row r="122">
@@ -1470,7 +1470,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>0.002291390538396396</v>
+        <v>0.001557589671400244</v>
       </c>
     </row>
     <row r="123">
@@ -1478,7 +1478,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>0.002290595105066287</v>
+        <v>0.001561996596149657</v>
       </c>
     </row>
     <row r="124">
@@ -1486,7 +1486,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>0.002288958138347927</v>
+        <v>0.001566331863586072</v>
       </c>
     </row>
     <row r="125">
@@ -1494,7 +1494,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>0.002287347574318573</v>
+        <v>0.001567596415767357</v>
       </c>
     </row>
     <row r="126">
@@ -1502,7 +1502,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>0.00228959721796929</v>
+        <v>0.001571113342386986</v>
       </c>
     </row>
     <row r="127">
@@ -1510,7 +1510,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>0.00229181115299063</v>
+        <v>0.001573397892465389</v>
       </c>
     </row>
     <row r="128">
@@ -1518,7 +1518,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>0.002290219767041031</v>
+        <v>0.001577773268856362</v>
       </c>
     </row>
     <row r="129">
@@ -1526,7 +1526,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>0.002288653246496894</v>
+        <v>0.001579878288439747</v>
       </c>
     </row>
     <row r="130">
@@ -1534,7 +1534,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>0.002282391851986761</v>
+        <v>0.001581825978843564</v>
       </c>
     </row>
     <row r="131">
@@ -1542,7 +1542,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>0.002276226786622939</v>
+        <v>0.001585367915085345</v>
       </c>
     </row>
     <row r="132">
@@ -1550,7 +1550,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>0.002280598844607584</v>
+        <v>0.00158875318337873</v>
       </c>
     </row>
     <row r="133">
@@ -1558,7 +1558,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>0.002282729054704555</v>
+        <v>0.001592087159728275</v>
       </c>
     </row>
     <row r="134">
@@ -1566,7 +1566,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>0.002284827231566984</v>
+        <v>0.001597296311327702</v>
       </c>
     </row>
     <row r="135">
@@ -1574,7 +1574,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>0.002286949878094914</v>
+        <v>0.001598455747643699</v>
       </c>
     </row>
     <row r="136">
@@ -1582,7 +1582,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>0.002289041078007615</v>
+        <v>0.001601189710151952</v>
       </c>
     </row>
     <row r="137">
@@ -1590,7 +1590,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>0.002294990947139596</v>
+        <v>0.001604264117354356</v>
       </c>
     </row>
     <row r="138">
@@ -1598,7 +1598,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>0.00230085395686819</v>
+        <v>0.001606792805560817</v>
       </c>
     </row>
     <row r="139">
@@ -1606,7 +1606,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>0.002304509866099582</v>
+        <v>0.00160708229700501</v>
       </c>
     </row>
     <row r="140">
@@ -1614,7 +1614,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>0.00230811317232045</v>
+        <v>0.001609122721985431</v>
       </c>
     </row>
     <row r="141">
@@ -1622,7 +1622,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>0.002311855517158813</v>
+        <v>0.001613303601913815</v>
       </c>
     </row>
     <row r="142">
@@ -1630,7 +1630,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>0.002315544779091666</v>
+        <v>0.001617425178580804</v>
       </c>
     </row>
     <row r="143">
@@ -1638,7 +1638,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>0.002317584591133246</v>
+        <v>0.001622361432747545</v>
       </c>
     </row>
     <row r="144">
@@ -1646,7 +1646,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>0.002319595874335082</v>
+        <v>0.001626470498217792</v>
       </c>
     </row>
     <row r="145">
@@ -1654,7 +1654,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>0.002321579223048005</v>
+        <v>0.001629966556041484</v>
       </c>
     </row>
     <row r="146">
@@ -1662,7 +1662,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>0.002321399347686323</v>
+        <v>0.001631858832810977</v>
       </c>
     </row>
     <row r="147">
@@ -1670,7 +1670,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>0.002321221936370692</v>
+        <v>0.00163430034674867</v>
       </c>
     </row>
     <row r="148">
@@ -1678,7 +1678,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>0.002321046938814457</v>
+        <v>0.001636466566091633</v>
       </c>
     </row>
     <row r="149">
@@ -1686,7 +1686,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>0.002320874306090064</v>
+        <v>0.001637498019076093</v>
       </c>
     </row>
     <row r="150">
@@ -1694,7 +1694,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>0.002320290262928645</v>
+        <v>0.001638940734925493</v>
       </c>
     </row>
     <row r="151">
@@ -1702,7 +1702,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>0.002319714007009378</v>
+        <v>0.001642666363292519</v>
       </c>
     </row>
     <row r="152">
@@ -1710,7 +1710,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>0.002319145383618844</v>
+        <v>0.001643710832920909</v>
       </c>
     </row>
     <row r="153">
@@ -1718,7 +1718,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>0.002318584242115027</v>
+        <v>0.001643931277093693</v>
       </c>
     </row>
     <row r="154">
@@ -1726,7 +1726,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>0.002318333773688099</v>
+        <v>0.001646980574751217</v>
       </c>
     </row>
     <row r="155">
@@ -1734,7 +1734,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>0.002318086558097884</v>
+        <v>0.001646795607786298</v>
       </c>
     </row>
     <row r="156">
@@ -1742,7 +1742,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>0.002317842532386253</v>
+        <v>0.001648122792499716</v>
       </c>
     </row>
     <row r="157">
@@ -1750,7 +1750,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>0.002317916106861363</v>
+        <v>0.001648238723592095</v>
       </c>
     </row>
     <row r="158">
@@ -1758,7 +1758,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>0.002317988744082013</v>
+        <v>0.001649176772510325</v>
       </c>
     </row>
     <row r="159">
@@ -1766,7 +1766,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>0.002318060461844174</v>
+        <v>0.001650506648105267</v>
       </c>
     </row>
     <row r="160">
@@ -1774,7 +1774,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>0.002318131277496119</v>
+        <v>0.001650314209259847</v>
       </c>
     </row>
     <row r="161">
@@ -1782,7 +1782,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>0.002319546283653996</v>
+        <v>0.001650517227737992</v>
       </c>
     </row>
     <row r="162">
@@ -1790,7 +1790,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>0.002320943712095626</v>
+        <v>0.00165089982224714</v>
       </c>
     </row>
     <row r="163">
@@ -1798,7 +1798,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>0.002322739844320745</v>
+        <v>0.001651671892551005</v>
       </c>
     </row>
     <row r="164">
@@ -1806,7 +1806,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>0.002324100534004399</v>
+        <v>0.001651426907684909</v>
       </c>
     </row>
     <row r="165">
@@ -1814,7 +1814,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>0.002325444629911424</v>
+        <v>0.001653640013153168</v>
       </c>
     </row>
     <row r="166">
@@ -1822,7 +1822,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>0.002326772433746848</v>
+        <v>0.001655733557136938</v>
       </c>
     </row>
     <row r="167">
@@ -1830,7 +1830,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>0.002328084239945701</v>
+        <v>0.001656589210383116</v>
       </c>
     </row>
     <row r="168">
@@ -1838,7 +1838,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>0.002336001818929771</v>
+        <v>0.001658985486942699</v>
       </c>
     </row>
     <row r="169">
@@ -1846,7 +1846,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>0.002343825141021173</v>
+        <v>0.001659453449822748</v>
       </c>
     </row>
     <row r="170">
@@ -1854,7 +1854,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>0.002348712520160753</v>
+        <v>0.00166076925544997</v>
       </c>
     </row>
     <row r="171">
@@ -1862,7 +1862,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>0.00235354240072222</v>
+        <v>0.001663434208834819</v>
       </c>
     </row>
     <row r="172">
@@ -1870,7 +1870,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>0.002353084390749782</v>
+        <v>0.001665508740357732</v>
       </c>
     </row>
     <row r="173">
@@ -1878,7 +1878,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>0.002352036229827102</v>
+        <v>0.001667717357806863</v>
       </c>
     </row>
     <row r="174">
@@ -1886,7 +1886,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>0.002351000186371737</v>
+        <v>0.001668918593448898</v>
       </c>
     </row>
     <row r="175">
@@ -1894,7 +1894,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>0.002350393727118557</v>
+        <v>0.001669108118592932</v>
       </c>
     </row>
     <row r="176">
@@ -1902,7 +1902,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>0.002349794198828269</v>
+        <v>0.001670900543303318</v>
       </c>
     </row>
     <row r="177">
@@ -1910,7 +1910,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>0.002350472904403646</v>
+        <v>0.001671037700499289</v>
       </c>
     </row>
     <row r="178">
@@ -1918,7 +1918,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>0.00235114394098947</v>
+        <v>0.001671571402513578</v>
       </c>
     </row>
     <row r="179">
@@ -1926,7 +1926,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>0.002350427630237972</v>
+        <v>0.001672983700026897</v>
       </c>
     </row>
     <row r="180">
@@ -1934,7 +1934,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>0.002349123540551217</v>
+        <v>0.001673963088665605</v>
       </c>
     </row>
     <row r="181">
@@ -1942,7 +1942,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>0.002347833940749871</v>
+        <v>0.001674931595208327</v>
       </c>
     </row>
     <row r="182">
@@ -1950,7 +1950,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>0.002350473027198205</v>
+        <v>0.001675580524145159</v>
       </c>
     </row>
     <row r="183">
@@ -1958,7 +1958,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>0.002353083112696557</v>
+        <v>0.001676184393863832</v>
       </c>
     </row>
     <row r="184">
@@ -1966,7 +1966,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>0.002354063819056941</v>
+        <v>0.001676604667376408</v>
       </c>
     </row>
     <row r="185">
@@ -1974,7 +1974,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>0.002355033865565581</v>
+        <v>0.00167702037269863</v>
       </c>
     </row>
     <row r="186">
@@ -1982,7 +1982,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>0.002355714312954904</v>
+        <v>0.00167743158390926</v>
       </c>
     </row>
     <row r="187">
@@ -1990,7 +1990,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>0.002356387443705631</v>
+        <v>0.001680240950627157</v>
       </c>
     </row>
     <row r="188">
@@ -1998,7 +1998,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>0.002361406512484374</v>
+        <v>0.001681886378239419</v>
       </c>
     </row>
     <row r="189">
@@ -2006,7 +2006,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>0.002366372186914407</v>
+        <v>0.001683286049152523</v>
       </c>
     </row>
     <row r="190">
@@ -2014,7 +2014,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>0.002366895081716788</v>
+        <v>0.001684670908733213</v>
       </c>
     </row>
     <row r="191">
@@ -2022,7 +2022,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>0.002367412472363354</v>
+        <v>0.001685824907913648</v>
       </c>
     </row>
     <row r="192">
@@ -2030,7 +2030,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>0.002369575716295637</v>
+        <v>0.001686966823333031</v>
       </c>
     </row>
     <row r="193">
@@ -2038,7 +2038,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>0.00237007375581787</v>
+        <v>0.001687112979440377</v>
       </c>
     </row>
     <row r="194">
@@ -2046,7 +2046,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>0.002370566634308785</v>
+        <v>0.001687840297045726</v>
       </c>
     </row>
     <row r="195">
@@ -2054,7 +2054,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>0.002369464491690069</v>
+        <v>0.001688701172581704</v>
       </c>
     </row>
     <row r="196">
@@ -2062,7 +2062,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>0.002368373653098212</v>
+        <v>0.001688841334839258</v>
       </c>
     </row>
     <row r="197">
@@ -2070,7 +2070,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>0.002366246803211384</v>
+        <v>0.001689418014731052</v>
       </c>
     </row>
     <row r="198">
@@ -2078,7 +2078,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>0.002364141545709195</v>
+        <v>0.001690645701260792</v>
       </c>
     </row>
     <row r="199">
@@ -2086,7 +2086,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>0.002362100881779653</v>
+        <v>0.001691860986916494</v>
       </c>
     </row>
     <row r="200">
@@ -2094,7 +2094,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>0.002360080727035332</v>
+        <v>0.001692245889063488</v>
       </c>
     </row>
     <row r="201">
@@ -2102,7 +2102,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>0.002359077954265729</v>
+        <v>0.001691415952206511</v>
       </c>
     </row>
     <row r="202">
@@ -2110,7 +2110,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>0.002358085159334629</v>
+        <v>0.001689735741296009</v>
       </c>
     </row>
     <row r="203">
@@ -2118,7 +2118,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>0.002360000082944001</v>
+        <v>0.00168952849139176</v>
       </c>
     </row>
     <row r="204">
@@ -2126,7 +2126,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>0.002361896140310916</v>
+        <v>0.00168859775802858</v>
       </c>
     </row>
     <row r="205">
@@ -2134,7 +2134,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>0.002363773608880116</v>
+        <v>0.001687676722013501</v>
       </c>
     </row>
     <row r="206">
@@ -2142,7 +2142,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>0.002363062504810591</v>
+        <v>0.001686134043871156</v>
       </c>
     </row>
     <row r="207">
@@ -2150,7 +2150,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>0.002362358304664071</v>
+        <v>0.00168522207853286</v>
       </c>
     </row>
     <row r="208">
@@ -2158,7 +2158,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>0.002360413699313665</v>
+        <v>0.001684318924453871</v>
       </c>
     </row>
     <row r="209">
@@ -2166,7 +2166,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>0.002358487792091629</v>
+        <v>0.001682093135783728</v>
       </c>
     </row>
     <row r="210">
@@ -2174,7 +2174,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>0.002359082068447713</v>
+        <v>0.001679740001182025</v>
       </c>
     </row>
     <row r="211">
@@ -2182,7 +2182,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>0.002359670685028978</v>
+        <v>0.001678241141459365</v>
       </c>
     </row>
     <row r="212">
@@ -2190,7 +2190,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>0.00236001846938881</v>
+        <v>0.001676553892795457</v>
       </c>
     </row>
     <row r="213">
@@ -2198,7 +2198,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>0.002360362972764116</v>
+        <v>0.00167619110347309</v>
       </c>
     </row>
     <row r="214">
@@ -2206,7 +2206,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>0.002360787651697127</v>
+        <v>0.001678229927963038</v>
       </c>
     </row>
     <row r="215">
@@ -2214,7 +2214,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>0.00236243941487407</v>
+        <v>0.001681291227488082</v>
       </c>
     </row>
     <row r="216">
@@ -2222,7 +2222,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>0.002364075812812158</v>
+        <v>0.001687056240215762</v>
       </c>
     </row>
     <row r="217">
@@ -2230,7 +2230,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>0.00236784180159144</v>
+        <v>0.001689249478773781</v>
       </c>
     </row>
     <row r="218">
@@ -2238,7 +2238,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>0.00237157308079672</v>
+        <v>0.001691422503151543</v>
       </c>
     </row>
     <row r="219">
@@ -2246,7 +2246,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>0.002373996328743095</v>
+        <v>0.001694410353328308</v>
       </c>
     </row>
     <row r="220">
@@ -2254,7 +2254,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>0.00237639744657124</v>
+        <v>0.001695152459632918</v>
       </c>
     </row>
     <row r="221">
@@ -2262,7 +2262,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>0.002376947560712347</v>
+        <v>0.00169563937236518</v>
       </c>
     </row>
     <row r="222">
@@ -2270,7 +2270,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>0.002377492696444938</v>
+        <v>0.001698283118442995</v>
       </c>
     </row>
     <row r="223">
@@ -2278,7 +2278,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>0.002376692098797532</v>
+        <v>0.001705289133962416</v>
       </c>
     </row>
     <row r="224">
@@ -2286,7 +2286,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>0.002377142393765684</v>
+        <v>0.001708349070172485</v>
       </c>
     </row>
     <row r="225">
@@ -2294,7 +2294,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="n">
-        <v>0.002377588668243049</v>
+        <v>0.001717188913995224</v>
       </c>
     </row>
     <row r="226">
@@ -2302,7 +2302,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>0.002379524100000372</v>
+        <v>0.001721079359124351</v>
       </c>
     </row>
     <row r="227">
@@ -2310,7 +2310,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>0.002381442404043029</v>
+        <v>0.001724935375535521</v>
       </c>
     </row>
     <row r="228">
@@ -2318,7 +2318,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>0.002383191935536899</v>
+        <v>0.001729368361871474</v>
       </c>
     </row>
     <row r="229">
@@ -2326,7 +2326,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>0.002384926120263281</v>
+        <v>0.001732487753274094</v>
       </c>
     </row>
     <row r="230">
@@ -2334,7 +2334,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>0.002382986842683567</v>
+        <v>0.00173538152492576</v>
       </c>
     </row>
     <row r="231">
@@ -2342,7 +2342,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>0.002382294731933126</v>
+        <v>0.001736105393884735</v>
       </c>
     </row>
     <row r="232">
@@ -2350,7 +2350,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>0.002381608613483555</v>
+        <v>0.001737288355972031</v>
       </c>
     </row>
     <row r="233">
@@ -2358,7 +2358,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>0.002382082338977962</v>
+        <v>0.001737514301298781</v>
       </c>
     </row>
     <row r="234">
@@ -2366,7 +2366,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>0.002382551998159113</v>
+        <v>0.00173677022456941</v>
       </c>
     </row>
     <row r="235">
@@ -2374,7 +2374,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>0.002383017643159228</v>
+        <v>0.001735021013229959</v>
       </c>
     </row>
     <row r="236">
@@ -2382,7 +2382,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>0.002383479325223172</v>
+        <v>0.001732821594613177</v>
       </c>
     </row>
     <row r="237">
@@ -2390,7 +2390,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>0.002383937094727252</v>
+        <v>0.00173032374088323</v>
       </c>
     </row>
     <row r="238">
@@ -2398,7 +2398,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>0.002384391001197542</v>
+        <v>0.001727876736230033</v>
       </c>
     </row>
     <row r="239">
@@ -2406,7 +2406,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>0.002384841093327746</v>
+        <v>0.001725497226395381</v>
       </c>
     </row>
     <row r="240">
@@ -2414,7 +2414,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>0.002384015313592623</v>
+        <v>0.001723456569311649</v>
       </c>
     </row>
     <row r="241">
@@ -2422,7 +2422,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>0.002383196415355293</v>
+        <v>0.00172134277680928</v>
       </c>
     </row>
     <row r="242">
@@ -2430,7 +2430,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>0.002383522081186843</v>
+        <v>0.001719569759544621</v>
       </c>
     </row>
     <row r="243">
@@ -2438,7 +2438,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>0.002383845055565238</v>
+        <v>0.001717239347472498</v>
       </c>
     </row>
     <row r="244">
@@ -2446,7 +2446,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="n">
-        <v>0.002384165371718298</v>
+        <v>0.001715098008550827</v>
       </c>
     </row>
     <row r="245">
@@ -2454,7 +2454,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>0.002384483062329119</v>
+        <v>0.001712886178852372</v>
       </c>
     </row>
     <row r="246">
@@ -2462,7 +2462,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>0.002380097981709516</v>
+        <v>0.001710506916004184</v>
       </c>
     </row>
     <row r="247">
@@ -2470,7 +2470,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>0.00237574855215186</v>
+        <v>0.001708564966779314</v>
       </c>
     </row>
     <row r="248">
@@ -2478,7 +2478,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>0.002375358135938439</v>
+        <v>0.001706238705026738</v>
       </c>
     </row>
     <row r="249">
@@ -2486,7 +2486,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>0.002374970868242868</v>
+        <v>0.001703850888297386</v>
       </c>
     </row>
     <row r="250">
@@ -2494,7 +2494,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>0.002374586711131197</v>
+        <v>0.001701729100017203</v>
       </c>
     </row>
     <row r="251">
@@ -2502,7 +2502,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="n">
-        <v>0.00237420562727642</v>
+        <v>0.001699620522599159</v>
       </c>
     </row>
     <row r="252">
@@ -2510,7 +2510,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="n">
-        <v>0.002373329369936933</v>
+        <v>0.001697505992040661</v>
       </c>
     </row>
     <row r="253">
@@ -2518,7 +2518,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>0.002373793714493365</v>
+        <v>0.00169521991345525</v>
       </c>
     </row>
     <row r="254">
@@ -2526,7 +2526,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>0.00237425438834184</v>
+        <v>0.001693048091458377</v>
       </c>
     </row>
     <row r="255">
@@ -2534,7 +2534,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>0.002373876699821926</v>
+        <v>0.001690992723715379</v>
       </c>
     </row>
     <row r="256">
@@ -2542,7 +2542,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>0.002373501973564914</v>
+        <v>0.001688762719827187</v>
       </c>
     </row>
     <row r="257">
@@ -2550,7 +2550,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>0.002376031853159257</v>
+        <v>0.001686523589836526</v>
       </c>
     </row>
     <row r="258">
@@ -2558,7 +2558,2607 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>0.002378542044974655</v>
+        <v>0.001684415686430663</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>0.001682327759733369</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>0.001680323432776179</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>0.001678368336778665</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>0.001676912762195759</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>0.001675126332310505</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>0.001673509837822682</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>0.001671761336954892</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>0.00166999517732113</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>0.001668240608083203</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>0.001666840895617984</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>0.001665180522697811</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>0.001663648008681691</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>0.001661863538643423</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>0.001660207038596393</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>0.0016585933390661</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>0.001656991461510389</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>0.001655654987593361</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="n">
+        <v>0.00165474726998123</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="n">
+        <v>0.00165345024899388</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="n">
+        <v>0.001653805402742867</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="n">
+        <v>0.001652362004784253</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="n">
+        <v>0.001651114970720067</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="n">
+        <v>0.001649932245770996</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="n">
+        <v>0.00164845608750577</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="n">
+        <v>0.001647914936202512</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="n">
+        <v>0.001647377609290089</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="n">
+        <v>0.001646206781973268</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="n">
+        <v>0.001644473992635314</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="n">
+        <v>0.001642904546232524</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="n">
+        <v>0.001641471779272497</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>0.001640279140452975</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>0.001638620764774784</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>0.001637383526439846</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>0.001637872218945634</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>0.001638357564242479</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>0.001638729917096218</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>0.001637957343829906</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>0.001636513264220867</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="n">
+        <v>0.00163528623908952</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="n">
+        <v>0.001634463696763558</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>0.001633288768048529</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>0.001633712412098962</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>0.001632333343495916</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>0.001630963438139403</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>0.001629815912997663</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>0.001628561861596549</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>0.001628218231394733</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>0.001628662525531938</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>0.001627953936469594</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>0.001626782032382796</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>0.001626144826217376</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>0.001626008209180801</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>0.001625251918325018</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>0.001624500491076024</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>0.001623013649700251</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>0.001623260131682456</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>0.001622433032718285</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>0.001621429405656843</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="n">
+        <v>0.001620469187087043</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="n">
+        <v>0.001619201780727414</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="n">
+        <v>0.001618084193958341</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="n">
+        <v>0.001617149519679366</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="n">
+        <v>0.001616163371988896</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="n">
+        <v>0.001615617839777126</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="n">
+        <v>0.001614382576234996</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="n">
+        <v>0.001613036369555715</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="n">
+        <v>0.001611879053830704</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="n">
+        <v>0.001611037639821277</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="n">
+        <v>0.001610201387860988</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="n">
+        <v>0.001609326705836575</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="n">
+        <v>0.00160845735723914</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="n">
+        <v>0.001606949129304538</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="n">
+        <v>0.001605759875471729</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="n">
+        <v>0.001604868189158162</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="n">
+        <v>0.001603714948669275</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="n">
+        <v>0.001603627418456366</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="n">
+        <v>0.001603081101250967</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="n">
+        <v>0.001603090441191455</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="n">
+        <v>0.00160282545659046</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="n">
+        <v>0.001602525702136837</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="n">
+        <v>0.00160155383174929</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="n">
+        <v>0.001600693773472984</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="n">
+        <v>0.001599887255721377</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="n">
+        <v>0.001599010389301123</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="n">
+        <v>0.001598138650754671</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="n">
+        <v>0.001597028463022993</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="n">
+        <v>0.00159592472987115</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="n">
+        <v>0.001594827395172362</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="n">
+        <v>0.001593736403448711</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="n">
+        <v>0.001592835652198995</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="n">
+        <v>0.001591940077680599</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="n">
+        <v>0.001591049635394401</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="n">
+        <v>0.001590163049780849</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="n">
+        <v>0.001589650545303665</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="n">
+        <v>0.001588738162725631</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="n">
+        <v>0.001588047168255379</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="n">
+        <v>0.001586738844347514</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="n">
+        <v>0.001585337609174424</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="n">
+        <v>0.001584497062333804</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="n">
+        <v>0.001583563664211245</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="n">
+        <v>0.00158325480553988</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="n">
+        <v>0.001582429202855185</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="n">
+        <v>0.001581393450593504</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="n">
+        <v>0.001580834114966217</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="n">
+        <v>0.00157980210704713</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="n">
+        <v>0.001578970295439184</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="n">
+        <v>0.001578720173057925</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="n">
+        <v>0.001578078942727526</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="n">
+        <v>0.001577441216388003</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="n">
+        <v>0.001577162712087116</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="n">
+        <v>0.00157666538077156</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="n">
+        <v>0.001577053947556349</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="n">
+        <v>0.00157642417106514</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="n">
+        <v>0.001575891671067173</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="n">
+        <v>0.001575278900164301</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="n">
+        <v>0.001574714045457254</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="n">
+        <v>0.001574232253240516</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="n">
+        <v>0.001573742036521692</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="n">
+        <v>0.00157292155800774</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="n">
+        <v>0.001572105432164948</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="n">
+        <v>0.001571551414046178</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="n">
+        <v>0.001571133985271967</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="n">
+        <v>0.001570516029908141</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="n">
+        <v>0.001569901318404492</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="n">
+        <v>0.001569608259738602</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="n">
+        <v>0.001570274866713203</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="n">
+        <v>0.001569986916346857</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="n">
+        <v>0.00156948812469023</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="n">
+        <v>0.001568991917446331</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="n">
+        <v>0.001568715672928849</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="n">
+        <v>0.001569608458517331</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="n">
+        <v>0.001570924192503969</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="n">
+        <v>0.001571734329283111</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="n">
+        <v>0.001571740745114364</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="n">
+        <v>0.001572475242312954</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="n">
+        <v>0.001571984530804578</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="n">
+        <v>0.001571735296432473</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="n">
+        <v>0.001571487324006556</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="n">
+        <v>0.001570844851098283</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="n">
+        <v>0.001570205614829347</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="n">
+        <v>0.001569724455799737</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="n">
+        <v>0.001569091231730892</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="n">
+        <v>0.001568461173782391</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="n">
+        <v>0.001567779992121056</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="n">
+        <v>0.001567129791733831</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="n">
+        <v>0.001566379409864868</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>0.001566101173631363</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>0.001565824311403949</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>0.001566614529521915</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>0.001567400864504166</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>0.00156735285058888</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>0.001566579738003535</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>0.001566153958391469</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" t="n">
+        <v>0.001565473456078223</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" t="n">
+        <v>0.001564796257174265</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" t="n">
+        <v>0.001564576008364477</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" t="n">
+        <v>0.0015643568235586</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" t="n">
+        <v>0.001563806059729732</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" t="n">
+        <v>0.001563504694051698</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" t="n">
+        <v>0.001563204773772599</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="n">
+        <v>0.00156440576453761</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="n">
+        <v>0.001564711287329354</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="n">
+        <v>0.001564618073695424</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="n">
+        <v>0.001564310592410682</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="n">
+        <v>0.001563844646627674</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="n">
+        <v>0.00156302244563793</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="n">
+        <v>0.001562865914969971</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="n">
+        <v>0.001563296533363093</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="n">
+        <v>0.001562875985937745</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="n">
+        <v>0.001562457408289564</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="n">
+        <v>0.001561990985678257</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="n">
+        <v>0.001561424712615882</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="n">
+        <v>0.001561067775598903</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="n">
+        <v>0.0015611441773093</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" t="n">
+        <v>0.001560366020823989</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" t="n">
+        <v>0.001560795695411352</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" t="n">
+        <v>0.001560704705068421</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" t="n">
+        <v>0.001560298047436669</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" t="n">
+        <v>0.001559715559142666</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" t="n">
+        <v>0.001559135736698978</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" t="n">
+        <v>0.001558558561846357</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="n">
+        <v>0.001557984016491926</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="n">
+        <v>0.001557412082707288</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" t="n">
+        <v>0.001556969646277505</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" t="n">
+        <v>0.001556529211822517</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" t="n">
+        <v>0.001555991856271787</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" t="n">
+        <v>0.001555656508658379</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" t="n">
+        <v>0.001556278944790409</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" t="n">
+        <v>0.001556262055082838</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" t="n">
+        <v>0.001555641250127348</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" t="n">
+        <v>0.001555502320800478</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" t="n">
+        <v>0.001555524473758505</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" t="n">
+        <v>0.001555268699772857</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" t="n">
+        <v>0.001555457071277533</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" t="n">
+        <v>0.001554863194473692</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" t="n">
+        <v>0.001554999520387062</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" t="n">
+        <v>0.001554869931606913</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" t="n">
+        <v>0.001554740912447776</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" t="n">
+        <v>0.001554426883580857</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" t="n">
+        <v>0.001554299096737239</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" t="n">
+        <v>0.001554301332436323</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" t="n">
+        <v>0.001554781347611315</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" t="n">
+        <v>0.001554393500572287</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" t="n">
+        <v>0.001554381735254383</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" t="n">
+        <v>0.001554370020868591</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" t="n">
+        <v>0.001554106394179897</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" t="n">
+        <v>0.001554281381187489</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" t="n">
+        <v>0.001555086158546433</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" t="n">
+        <v>0.001555735067862784</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" t="n">
+        <v>0.001555764501880322</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" t="n">
+        <v>0.001555627281802528</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" t="n">
+        <v>0.001556463215528549</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" t="n">
+        <v>0.001556289374959791</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" t="n">
+        <v>0.001556116272567546</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" t="n">
+        <v>0.001555933829099291</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" t="n">
+        <v>0.001556256843703852</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" t="n">
+        <v>0.001555946808892719</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" t="n">
+        <v>0.001555308872468018</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" t="n">
+        <v>0.001556034108035553</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" t="n">
+        <v>0.001556331606114908</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" t="n">
+        <v>0.001556627859432425</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" t="n">
+        <v>0.001556922875784107</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" t="n">
+        <v>0.00155721666290099</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" t="n">
+        <v>0.001557639123879345</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" t="n">
+        <v>0.001557804819402547</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" t="n">
+        <v>0.001558527082853096</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" t="n">
+        <v>0.001558185935729058</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" t="n">
+        <v>0.001558624148265256</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" t="n">
+        <v>0.001559294163208007</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" t="n">
+        <v>0.001559090022343198</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" t="n">
+        <v>0.001559131070476536</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" t="n">
+        <v>0.001559083969397784</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" t="n">
+        <v>0.001559037060568332</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" t="n">
+        <v>0.00155965210628782</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" t="n">
+        <v>0.001560542273749203</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" t="n">
+        <v>0.001561543331908386</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" t="n">
+        <v>0.001560838081510099</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" t="n">
+        <v>0.001561637691109953</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" t="n">
+        <v>0.001562114732564435</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" t="n">
+        <v>0.001563749350519488</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" t="n">
+        <v>0.001563860233391887</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" t="n">
+        <v>0.001565701384422661</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" t="n">
+        <v>0.00156580998151063</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" t="n">
+        <v>0.001567833579898271</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" t="n">
+        <v>0.001567968174041767</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" t="n">
+        <v>0.001570291402718004</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" t="n">
+        <v>0.001572197312378185</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" t="n">
+        <v>0.001572152940042505</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" t="n">
+        <v>0.001574586658455659</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" t="n">
+        <v>0.001574705350189393</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" t="n">
+        <v>0.001574653398956112</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" t="n">
+        <v>0.001575560888330787</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" t="n">
+        <v>0.001576547889199076</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>511</v>
+      </c>
+      <c r="B512" t="n">
+        <v>0.001577103350193339</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>512</v>
+      </c>
+      <c r="B513" t="n">
+        <v>0.001577428838069549</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>513</v>
+      </c>
+      <c r="B514" t="n">
+        <v>0.001577911898330786</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>514</v>
+      </c>
+      <c r="B515" t="n">
+        <v>0.001577514558949726</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>515</v>
+      </c>
+      <c r="B516" t="n">
+        <v>0.001577426849935436</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>516</v>
+      </c>
+      <c r="B517" t="n">
+        <v>0.001577364924673314</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>517</v>
+      </c>
+      <c r="B518" t="n">
+        <v>0.001579697152820497</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>518</v>
+      </c>
+      <c r="B519" t="n">
+        <v>0.001579728593891988</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>519</v>
+      </c>
+      <c r="B520" t="n">
+        <v>0.001581965009914524</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>520</v>
+      </c>
+      <c r="B521" t="n">
+        <v>0.001587693120546262</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>521</v>
+      </c>
+      <c r="B522" t="n">
+        <v>0.001590331481216529</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>522</v>
+      </c>
+      <c r="B523" t="n">
+        <v>0.001596038912736472</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>523</v>
+      </c>
+      <c r="B524" t="n">
+        <v>0.001598226061734598</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>524</v>
+      </c>
+      <c r="B525" t="n">
+        <v>0.00160385657000874</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>525</v>
+      </c>
+      <c r="B526" t="n">
+        <v>0.001606260164354075</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>526</v>
+      </c>
+      <c r="B527" t="n">
+        <v>0.001606708176104893</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>527</v>
+      </c>
+      <c r="B528" t="n">
+        <v>0.00160753240820687</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>528</v>
+      </c>
+      <c r="B529" t="n">
+        <v>0.001610251260696799</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>529</v>
+      </c>
+      <c r="B530" t="n">
+        <v>0.001621469121117615</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>530</v>
+      </c>
+      <c r="B531" t="n">
+        <v>0.001629559577613159</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>531</v>
+      </c>
+      <c r="B532" t="n">
+        <v>0.001640590030931335</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>532</v>
+      </c>
+      <c r="B533" t="n">
+        <v>0.0016486614803179</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>533</v>
+      </c>
+      <c r="B534" t="n">
+        <v>0.001657343998229189</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>534</v>
+      </c>
+      <c r="B535" t="n">
+        <v>0.001663359772871948</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>535</v>
+      </c>
+      <c r="B536" t="n">
+        <v>0.001671109631846725</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" t="n">
+        <v>0.001678939872769521</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" t="n">
+        <v>0.001684016655151483</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" t="n">
+        <v>0.00168826771098879</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" t="n">
+        <v>0.001696944249541393</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" t="n">
+        <v>0.001700591342869475</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" t="n">
+        <v>0.001703900806141956</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" t="n">
+        <v>0.001709271768766607</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" t="n">
+        <v>0.001712650601526734</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" t="n">
+        <v>0.001716323467152448</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" t="n">
+        <v>0.001719518703434828</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" t="n">
+        <v>0.001722702235555002</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>547</v>
+      </c>
+      <c r="B548" t="n">
+        <v>0.001725429818774357</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>548</v>
+      </c>
+      <c r="B549" t="n">
+        <v>0.001728291775442865</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>549</v>
+      </c>
+      <c r="B550" t="n">
+        <v>0.001730214768743952</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>550</v>
+      </c>
+      <c r="B551" t="n">
+        <v>0.001735284704723601</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>551</v>
+      </c>
+      <c r="B552" t="n">
+        <v>0.001739524530463078</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>552</v>
+      </c>
+      <c r="B553" t="n">
+        <v>0.001742326708783425</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>553</v>
+      </c>
+      <c r="B554" t="n">
+        <v>0.001745755299388852</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>554</v>
+      </c>
+      <c r="B555" t="n">
+        <v>0.001747926272514479</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>555</v>
+      </c>
+      <c r="B556" t="n">
+        <v>0.001749501706322842</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>556</v>
+      </c>
+      <c r="B557" t="n">
+        <v>0.001751071473103117</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>557</v>
+      </c>
+      <c r="B558" t="n">
+        <v>0.00175238398562712</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>558</v>
+      </c>
+      <c r="B559" t="n">
+        <v>0.001754741314270143</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>559</v>
+      </c>
+      <c r="B560" t="n">
+        <v>0.00175872767121691</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>560</v>
+      </c>
+      <c r="B561" t="n">
+        <v>0.001761874362481517</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>561</v>
+      </c>
+      <c r="B562" t="n">
+        <v>0.001764263441144745</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>562</v>
+      </c>
+      <c r="B563" t="n">
+        <v>0.001766450649553557</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>563</v>
+      </c>
+      <c r="B564" t="n">
+        <v>0.001768375994351268</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>564</v>
+      </c>
+      <c r="B565" t="n">
+        <v>0.001770379694243935</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>565</v>
+      </c>
+      <c r="B566" t="n">
+        <v>0.00177237630139362</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" t="n">
+        <v>0.001775788426282495</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>567</v>
+      </c>
+      <c r="B568" t="n">
+        <v>0.001779368787663476</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>568</v>
+      </c>
+      <c r="B569" t="n">
+        <v>0.001782653949355968</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>569</v>
+      </c>
+      <c r="B570" t="n">
+        <v>0.001785360469650842</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>570</v>
+      </c>
+      <c r="B571" t="n">
+        <v>0.00178802822826852</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>571</v>
+      </c>
+      <c r="B572" t="n">
+        <v>0.001788780055382119</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>572</v>
+      </c>
+      <c r="B573" t="n">
+        <v>0.001791006837043103</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>573</v>
+      </c>
+      <c r="B574" t="n">
+        <v>0.001793297651184647</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>574</v>
+      </c>
+      <c r="B575" t="n">
+        <v>0.001795580483395384</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>575</v>
+      </c>
+      <c r="B576" t="n">
+        <v>0.001797711508537452</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>576</v>
+      </c>
+      <c r="B577" t="n">
+        <v>0.001801628231592417</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>577</v>
+      </c>
+      <c r="B578" t="n">
+        <v>0.001805130617715534</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>578</v>
+      </c>
+      <c r="B579" t="n">
+        <v>0.001807296424494738</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>579</v>
+      </c>
+      <c r="B580" t="n">
+        <v>0.001810440159487295</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>580</v>
+      </c>
+      <c r="B581" t="n">
+        <v>0.001817154242828901</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>581</v>
+      </c>
+      <c r="B582" t="n">
+        <v>0.001820066841707566</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>582</v>
+      </c>
+      <c r="B583" t="n">
+        <v>0.001825163413606268</v>
       </c>
     </row>
   </sheetData>
